--- a/docs/oc-regiones/pasajes-aereos-nacionales/lib-gral-bdo-o-higgins.xlsx
+++ b/docs/oc-regiones/pasajes-aereos-nacionales/lib-gral-bdo-o-higgins.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>482.83</v>
+        <v>478.74</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>397.13</v>
+        <v>395.09</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>370.95</v>
+        <v>369.04</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>563.76</v>
+        <v>558.13</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>405.52</v>
+        <v>401.47</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>217.69</v>
+        <v>215.52</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>380.24</v>
+        <v>376.45</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>135.93</v>
+        <v>135.19</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>146.84</v>
+        <v>146.04</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>105.24</v>
+        <v>104.67</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>279.41</v>
+        <v>277.89</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>627.87</v>
+        <v>624.4400000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>240.03</v>
+        <v>238.72</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>258.41</v>
+        <v>255.53</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>185.83</v>
+        <v>183.76</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>218.71</v>
+        <v>216.27</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>189.05</v>
+        <v>186.95</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>261.35</v>
+        <v>258.44</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>865.87</v>
+        <v>856.22</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>144.25</v>
+        <v>142.64</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>305.38</v>
+        <v>301.98</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>742</v>
+        <v>733.73</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>487.76</v>
+        <v>482.32</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>447.27</v>
+        <v>444.82</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>108.09</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>747.02</v>
+        <v>742.9299999999999</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>76.36</v>
+        <v>76.26000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>352.73</v>
+        <v>353.98</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1083.14</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>556.8</v>
+        <v>558.78</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>944.73</v>
+        <v>948.1</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>700.85</v>
+        <v>708.48</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>289.77</v>
+        <v>292.92</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>143.95</v>
+        <v>145.52</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>939.39</v>
+        <v>949.6</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>560.86</v>
+        <v>566.96</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>196.16</v>
+        <v>198.29</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>597.41</v>
+        <v>603.91</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>372.55</v>
+        <v>373.78</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>118.08</v>
+        <v>118.47</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>337.59</v>
+        <v>343.42</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>238.8</v>
+        <v>242.92</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>249.09</v>
+        <v>253.39</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>190.28</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>475.79</v>
+        <v>479.08</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>313.13</v>
+        <v>315.39</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>250.72</v>
+        <v>252.53</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>288.55</v>
+        <v>290.63</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>332.42</v>
+        <v>331.05</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>144.51</v>
+        <v>143.92</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>218.98</v>
+        <v>218.08</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>370.04</v>
+        <v>368.51</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>156.78</v>
+        <v>156.13</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>527.72</v>
+        <v>525.55</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>454.25</v>
+        <v>452.38</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>153.73</v>
+        <v>153.49</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>375.44</v>
+        <v>374.85</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>167.24</v>
+        <v>166.98</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>798.86</v>
+        <v>802.98</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>437.96</v>
+        <v>440.22</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>434.12</v>
+        <v>436.36</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>464.89</v>
+        <v>468.17</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>713.04</v>
+        <v>718.08</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>173.38</v>
+        <v>171.18</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>681.91</v>
+        <v>673.25</v>
       </c>
     </row>
     <row r="67">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>48.63</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="68">
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>270.26</v>
+        <v>266.82</v>
       </c>
     </row>
     <row r="69">
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>344.58</v>
+        <v>341.15</v>
       </c>
     </row>
     <row r="70">
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>58.67</v>
+        <v>58.09</v>
       </c>
     </row>
     <row r="71">
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>116.24</v>
+        <v>115.99</v>
       </c>
     </row>
     <row r="72">
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>50.75</v>
+        <v>50.64</v>
       </c>
     </row>
     <row r="73">
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>79.23999999999999</v>
+        <v>79.06999999999999</v>
       </c>
     </row>
     <row r="74">
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>283.24</v>
+        <v>282.63</v>
       </c>
     </row>
     <row r="75">
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>240.02</v>
+        <v>239.5</v>
       </c>
     </row>
     <row r="76">
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>188.93</v>
+        <v>188.52</v>
       </c>
     </row>
     <row r="77">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>782.22</v>
+        <v>778.9400000000001</v>
       </c>
     </row>
     <row r="78">
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1291.04</v>
+        <v>1285.63</v>
       </c>
     </row>
     <row r="79">
@@ -5274,7 +5274,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>269.73</v>
+        <v>268.6</v>
       </c>
     </row>
     <row r="80">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>204</v>
+        <v>203.14</v>
       </c>
     </row>
     <row r="81">
@@ -5396,7 +5396,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>562.03</v>
+        <v>555.53</v>
       </c>
     </row>
     <row r="82">
@@ -5457,7 +5457,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>537.3099999999999</v>
+        <v>531.09</v>
       </c>
     </row>
     <row r="83">
@@ -5518,7 +5518,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>144.73</v>
+        <v>143.05</v>
       </c>
     </row>
     <row r="84">
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>168.57</v>
+        <v>167.14</v>
       </c>
     </row>
     <row r="85">
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>388.35</v>
+        <v>389.84</v>
       </c>
     </row>
     <row r="86">
@@ -5701,7 +5701,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>93.98</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="87">
@@ -5762,7 +5762,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>122.46</v>
+        <v>122.79</v>
       </c>
     </row>
     <row r="88">
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>281.56</v>
+        <v>281.92</v>
       </c>
     </row>
     <row r="89">
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1630.96</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="90">
@@ -5945,7 +5945,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>815.48</v>
+        <v>825.5</v>
       </c>
     </row>
     <row r="91">
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>317.36</v>
+        <v>319.09</v>
       </c>
     </row>
     <row r="92">
@@ -6067,7 +6067,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>88.08</v>
+        <v>88.56</v>
       </c>
     </row>
     <row r="93">
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>774.15</v>
+        <v>778.38</v>
       </c>
     </row>
     <row r="94">
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>372.32</v>
+        <v>374.35</v>
       </c>
     </row>
     <row r="95">
@@ -6250,7 +6250,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>183.36</v>
+        <v>184.36</v>
       </c>
     </row>
     <row r="96">
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>230.04</v>
+        <v>231.3</v>
       </c>
     </row>
     <row r="97">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>687.64</v>
+        <v>677.79</v>
       </c>
     </row>
     <row r="98">
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>370.59</v>
+        <v>365.25</v>
       </c>
     </row>
     <row r="99">
@@ -6494,7 +6494,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>869.25</v>
+        <v>856.72</v>
       </c>
     </row>
     <row r="100">
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>271.27</v>
+        <v>267.36</v>
       </c>
     </row>
     <row r="101">
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>455.64</v>
+        <v>449.07</v>
       </c>
     </row>
     <row r="102">
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>247.74</v>
+        <v>244.17</v>
       </c>
     </row>
     <row r="103">
@@ -6738,7 +6738,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>373.42</v>
+        <v>368.59</v>
       </c>
     </row>
     <row r="104">
@@ -6799,7 +6799,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>379.83</v>
+        <v>374.92</v>
       </c>
     </row>
     <row r="105">
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>645.8200000000001</v>
+        <v>637.47</v>
       </c>
     </row>
     <row r="106">
@@ -6921,7 +6921,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>519.49</v>
+        <v>518.46</v>
       </c>
     </row>
     <row r="107">
@@ -7043,7 +7043,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>406.43</v>
+        <v>406.99</v>
       </c>
     </row>
     <row r="109">
@@ -7104,7 +7104,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1584.24</v>
+        <v>1586.44</v>
       </c>
     </row>
     <row r="110">
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>824.03</v>
+        <v>823.47</v>
       </c>
     </row>
     <row r="111">
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>393.47</v>
+        <v>393.2</v>
       </c>
     </row>
     <row r="112">
@@ -7287,7 +7287,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1045.66</v>
+        <v>1044.94</v>
       </c>
     </row>
     <row r="113">
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>315.91</v>
+        <v>315.69</v>
       </c>
     </row>
     <row r="114">
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>237.97</v>
+        <v>237.16</v>
       </c>
     </row>
     <row r="115">
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>298.05</v>
+        <v>297.03</v>
       </c>
     </row>
     <row r="116">
@@ -7531,7 +7531,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>375.87</v>
+        <v>373.88</v>
       </c>
     </row>
     <row r="117">
@@ -7592,7 +7592,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>509.42</v>
+        <v>506.23</v>
       </c>
     </row>
     <row r="118">
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>599.75</v>
+        <v>603.6799999999999</v>
       </c>
     </row>
     <row r="119">
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1352.9</v>
+        <v>1361.77</v>
       </c>
     </row>
     <row r="120">
@@ -7775,7 +7775,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>247.93</v>
+        <v>249.55</v>
       </c>
     </row>
     <row r="121">
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>230.45</v>
+        <v>231.96</v>
       </c>
     </row>
     <row r="122">
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>183.23</v>
+        <v>186.02</v>
       </c>
     </row>
     <row r="123">
@@ -7958,7 +7958,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>327.17</v>
+        <v>335.44</v>
       </c>
     </row>
     <row r="124">
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>219.91</v>
+        <v>225.47</v>
       </c>
     </row>
     <row r="125">
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>166.65</v>
+        <v>167.13</v>
       </c>
     </row>
     <row r="126">
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>216.24</v>
+        <v>216.87</v>
       </c>
     </row>
     <row r="127">
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>203.25</v>
+        <v>203.84</v>
       </c>
     </row>
     <row r="128">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>181.42</v>
+        <v>182.35</v>
       </c>
     </row>
     <row r="129">
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>170.82</v>
+        <v>171.29</v>
       </c>
     </row>
     <row r="130">
@@ -8389,7 +8389,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>45.42</v>
+        <v>45.84</v>
       </c>
     </row>
     <row r="131">
@@ -8450,7 +8450,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>118.68</v>
+        <v>119.76</v>
       </c>
     </row>
     <row r="132">
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>220.63</v>
+        <v>222.63</v>
       </c>
     </row>
     <row r="133">
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>261.24</v>
+        <v>263.06</v>
       </c>
     </row>
     <row r="134">
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>673.8099999999999</v>
+        <v>670.14</v>
       </c>
     </row>
     <row r="135">
@@ -8694,7 +8694,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>339.52</v>
+        <v>337.67</v>
       </c>
     </row>
     <row r="136">
@@ -8755,7 +8755,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>165.66</v>
+        <v>164.76</v>
       </c>
     </row>
     <row r="137">
@@ -8816,7 +8816,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>157.83</v>
+        <v>156.97</v>
       </c>
     </row>
     <row r="138">
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>697.83</v>
+        <v>694.03</v>
       </c>
     </row>
     <row r="139">
@@ -8938,7 +8938,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>395.37</v>
+        <v>393.85</v>
       </c>
     </row>
     <row r="140">
@@ -8999,7 +8999,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>544.25</v>
+        <v>542.15</v>
       </c>
     </row>
     <row r="141">
@@ -9060,7 +9060,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>319.45</v>
+        <v>321.1</v>
       </c>
     </row>
     <row r="142">
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>999.6</v>
+        <v>1043.74</v>
       </c>
     </row>
     <row r="143">
@@ -9182,7 +9182,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>126.48</v>
+        <v>132.06</v>
       </c>
     </row>
     <row r="144">
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>252.57</v>
+        <v>253.56</v>
       </c>
     </row>
     <row r="145">
@@ -9304,7 +9304,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>266.42</v>
+        <v>267.47</v>
       </c>
     </row>
     <row r="146">
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>147.06</v>
+        <v>147.64</v>
       </c>
     </row>
     <row r="147">
@@ -9426,7 +9426,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>104.03</v>
+        <v>104.44</v>
       </c>
     </row>
     <row r="148">
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>535.39</v>
+        <v>544.22</v>
       </c>
     </row>
     <row r="149">
@@ -9548,7 +9548,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>183.33</v>
+        <v>186.35</v>
       </c>
     </row>
     <row r="150">
@@ -9609,7 +9609,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>171.46</v>
+        <v>171.88</v>
       </c>
     </row>
     <row r="151">
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>156.84</v>
+        <v>157.22</v>
       </c>
     </row>
     <row r="152">
@@ -9731,7 +9731,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>143.76</v>
+        <v>144.12</v>
       </c>
     </row>
     <row r="153">
@@ -9792,7 +9792,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>247.38</v>
+        <v>244.19</v>
       </c>
     </row>
     <row r="154">
@@ -9853,7 +9853,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>108.86</v>
+        <v>108.1</v>
       </c>
     </row>
     <row r="155">
@@ -9914,7 +9914,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>945.66</v>
+        <v>938.98</v>
       </c>
     </row>
     <row r="156">
@@ -9975,7 +9975,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>563.49</v>
+        <v>559.51</v>
       </c>
     </row>
     <row r="157">
@@ -10036,7 +10036,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1398.43</v>
+        <v>1388.56</v>
       </c>
     </row>
     <row r="158">
@@ -10097,7 +10097,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>286.57</v>
+        <v>284.55</v>
       </c>
     </row>
     <row r="159">
@@ -10158,7 +10158,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>171.07</v>
+        <v>173.75</v>
       </c>
     </row>
     <row r="160">
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>340.71</v>
+        <v>346.05</v>
       </c>
     </row>
     <row r="161">
@@ -10280,7 +10280,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>500.18</v>
+        <v>508.01</v>
       </c>
     </row>
     <row r="162">
@@ -10341,7 +10341,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>685.8200000000001</v>
+        <v>685.78</v>
       </c>
     </row>
     <row r="163">
@@ -10402,7 +10402,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>232.24</v>
+        <v>232.22</v>
       </c>
     </row>
     <row r="164">
@@ -10463,7 +10463,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>397.68</v>
+        <v>397.66</v>
       </c>
     </row>
     <row r="165">
@@ -10524,7 +10524,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>377.05</v>
+        <v>377.38</v>
       </c>
     </row>
     <row r="166">
@@ -10585,7 +10585,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>546.45</v>
+        <v>546.92</v>
       </c>
     </row>
     <row r="167">
@@ -10646,7 +10646,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>532.16</v>
+        <v>534.36</v>
       </c>
     </row>
     <row r="168">
@@ -10707,7 +10707,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>284.22</v>
+        <v>283.44</v>
       </c>
     </row>
     <row r="169">
@@ -10768,7 +10768,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>369.5</v>
+        <v>367.38</v>
       </c>
     </row>
     <row r="170">
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>326.56</v>
+        <v>321.84</v>
       </c>
     </row>
     <row r="171">
@@ -10890,7 +10890,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>125.76</v>
+        <v>123.94</v>
       </c>
     </row>
     <row r="172">
@@ -10951,7 +10951,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>133.38</v>
+        <v>131.45</v>
       </c>
     </row>
     <row r="173">
@@ -11012,7 +11012,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>88.53</v>
+        <v>87.25</v>
       </c>
     </row>
     <row r="174">
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>233.71</v>
+        <v>230.33</v>
       </c>
     </row>
     <row r="175">
@@ -11134,7 +11134,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>64.95999999999999</v>
+        <v>64.02</v>
       </c>
     </row>
     <row r="176">
@@ -11195,7 +11195,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>437.85</v>
+        <v>427.66</v>
       </c>
     </row>
     <row r="177">
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>395.64</v>
+        <v>386.43</v>
       </c>
     </row>
     <row r="178">
@@ -11317,7 +11317,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>532.05</v>
+        <v>515.08</v>
       </c>
     </row>
     <row r="179">
@@ -11378,7 +11378,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>222.84</v>
+        <v>218.45</v>
       </c>
     </row>
     <row r="180">
@@ -11439,7 +11439,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>84.87</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="181">
@@ -11500,7 +11500,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>318.09</v>
+        <v>311.82</v>
       </c>
     </row>
     <row r="182">
@@ -11561,7 +11561,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>101.8</v>
+        <v>99.79000000000001</v>
       </c>
     </row>
     <row r="183">
@@ -11622,7 +11622,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>162.73</v>
+        <v>159.52</v>
       </c>
     </row>
     <row r="184">
@@ -11683,7 +11683,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>219.66</v>
+        <v>215.33</v>
       </c>
     </row>
     <row r="185">
@@ -11744,7 +11744,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>142.23</v>
+        <v>139.42</v>
       </c>
     </row>
     <row r="186">
@@ -11805,7 +11805,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>158.04</v>
+        <v>154.93</v>
       </c>
     </row>
     <row r="187">
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>180.21</v>
+        <v>176.66</v>
       </c>
     </row>
     <row r="188">
@@ -11927,7 +11927,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>704.65</v>
+        <v>690.76</v>
       </c>
     </row>
     <row r="189">
@@ -11988,7 +11988,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>72.06999999999999</v>
+        <v>70.18000000000001</v>
       </c>
     </row>
     <row r="190">
@@ -12049,7 +12049,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>522.3200000000001</v>
+        <v>512.85</v>
       </c>
     </row>
     <row r="191">
@@ -12110,7 +12110,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>633.21</v>
+        <v>635.05</v>
       </c>
     </row>
     <row r="192">
@@ -12171,7 +12171,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>292.93</v>
+        <v>294.15</v>
       </c>
     </row>
     <row r="193">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>351.21</v>
+        <v>354.19</v>
       </c>
     </row>
     <row r="194">
@@ -12293,7 +12293,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>725.67</v>
+        <v>731.83</v>
       </c>
     </row>
     <row r="195">
@@ -12354,7 +12354,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>744.55</v>
+        <v>750.87</v>
       </c>
     </row>
     <row r="196">
@@ -12415,7 +12415,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>212.31</v>
+        <v>211.95</v>
       </c>
     </row>
     <row r="197">
@@ -12476,7 +12476,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>235.58</v>
+        <v>235.19</v>
       </c>
     </row>
     <row r="198">
@@ -12537,7 +12537,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>277.91</v>
+        <v>277.44</v>
       </c>
     </row>
     <row r="199">
@@ -12598,7 +12598,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>216.54</v>
+        <v>216.18</v>
       </c>
     </row>
     <row r="200">
@@ -12659,7 +12659,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>526.41</v>
+        <v>532.89</v>
       </c>
     </row>
     <row r="201">
@@ -12720,7 +12720,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>452.63</v>
+        <v>458.2</v>
       </c>
     </row>
     <row r="202">
@@ -12781,7 +12781,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>589.67</v>
+        <v>596.9299999999999</v>
       </c>
     </row>
     <row r="203">
@@ -12842,7 +12842,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>405.86</v>
+        <v>410.85</v>
       </c>
     </row>
     <row r="204">
@@ -12907,7 +12907,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>3.91</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="205">
@@ -12968,7 +12968,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>331.51</v>
+        <v>335.92</v>
       </c>
     </row>
     <row r="206">
@@ -13029,7 +13029,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>599.77</v>
+        <v>607.76</v>
       </c>
     </row>
     <row r="207">
@@ -13090,7 +13090,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>184.21</v>
+        <v>188.74</v>
       </c>
     </row>
     <row r="208">
@@ -13151,7 +13151,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>389.16</v>
+        <v>396.52</v>
       </c>
     </row>
     <row r="209">
@@ -13212,7 +13212,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>217.6</v>
+        <v>221.71</v>
       </c>
     </row>
     <row r="210">
@@ -13273,7 +13273,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>217.62</v>
+        <v>219.58</v>
       </c>
     </row>
     <row r="211">
@@ -13334,7 +13334,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>324.52</v>
+        <v>326.59</v>
       </c>
     </row>
     <row r="212">
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>155.56</v>
+        <v>156.55</v>
       </c>
     </row>
     <row r="213">
@@ -13456,7 +13456,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>289.54</v>
+        <v>290.74</v>
       </c>
     </row>
     <row r="214">
@@ -13517,7 +13517,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>904.4400000000001</v>
+        <v>906.3200000000001</v>
       </c>
     </row>
     <row r="215">
@@ -13578,7 +13578,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>241.63</v>
+        <v>242.13</v>
       </c>
     </row>
     <row r="216">
@@ -13639,7 +13639,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>212.31</v>
+        <v>212.75</v>
       </c>
     </row>
     <row r="217">
@@ -13700,7 +13700,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>533.03</v>
+        <v>534.14</v>
       </c>
     </row>
     <row r="218">
@@ -13761,7 +13761,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>644.75</v>
+        <v>641.98</v>
       </c>
     </row>
     <row r="219">
@@ -13822,7 +13822,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>186.97</v>
+        <v>184.42</v>
       </c>
     </row>
     <row r="220">
@@ -13883,7 +13883,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>179.97</v>
+        <v>178.43</v>
       </c>
     </row>
     <row r="221">
@@ -13944,7 +13944,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>495.82</v>
+        <v>491.59</v>
       </c>
     </row>
     <row r="222">
@@ -14005,7 +14005,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>423.67</v>
+        <v>425.96</v>
       </c>
     </row>
     <row r="223">
@@ -14066,7 +14066,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>117.12</v>
+        <v>117.75</v>
       </c>
     </row>
     <row r="224">
@@ -14127,7 +14127,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>405.14</v>
+        <v>407.32</v>
       </c>
     </row>
     <row r="225">
@@ -14188,7 +14188,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>973.16</v>
+        <v>984.04</v>
       </c>
     </row>
     <row r="226">
@@ -14249,7 +14249,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>411.81</v>
+        <v>416.41</v>
       </c>
     </row>
     <row r="227">
@@ -14310,7 +14310,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>395.33</v>
+        <v>396.83</v>
       </c>
     </row>
     <row r="228">
@@ -14371,7 +14371,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>540.9</v>
+        <v>542.95</v>
       </c>
     </row>
     <row r="229">
@@ -14432,7 +14432,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>233.53</v>
+        <v>232.94</v>
       </c>
     </row>
     <row r="230">
@@ -14493,7 +14493,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>875.1</v>
+        <v>872.89</v>
       </c>
     </row>
     <row r="231">
@@ -14554,7 +14554,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>154.98</v>
+        <v>154.59</v>
       </c>
     </row>
     <row r="232">
@@ -14615,7 +14615,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>511.07</v>
+        <v>509.78</v>
       </c>
     </row>
     <row r="233">
@@ -14676,7 +14676,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>396.21</v>
+        <v>395.21</v>
       </c>
     </row>
     <row r="234">
@@ -14737,7 +14737,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>673.78</v>
+        <v>672.08</v>
       </c>
     </row>
     <row r="235">
@@ -14798,7 +14798,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>214.83</v>
+        <v>214.29</v>
       </c>
     </row>
     <row r="236">
@@ -14859,7 +14859,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>316.28</v>
+        <v>319.29</v>
       </c>
     </row>
     <row r="237">
@@ -14920,7 +14920,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>165.41</v>
+        <v>166.98</v>
       </c>
     </row>
     <row r="238">
@@ -14981,7 +14981,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>174.59</v>
+        <v>176.25</v>
       </c>
     </row>
     <row r="239">
@@ -15042,7 +15042,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>770.38</v>
+        <v>777.7</v>
       </c>
     </row>
     <row r="240">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>251.84</v>
+        <v>253.71</v>
       </c>
     </row>
     <row r="241">
@@ -15164,7 +15164,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>1051.9</v>
+        <v>1059.74</v>
       </c>
     </row>
     <row r="242">
@@ -15225,7 +15225,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>1685.46</v>
+        <v>1698.02</v>
       </c>
     </row>
     <row r="243">
@@ -15286,7 +15286,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>109.88</v>
+        <v>110.69</v>
       </c>
     </row>
     <row r="244">
@@ -15347,7 +15347,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>129.93</v>
+        <v>129.36</v>
       </c>
     </row>
     <row r="245">
@@ -15408,7 +15408,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>136.2</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="246">
@@ -15469,7 +15469,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>524.63</v>
+        <v>522.33</v>
       </c>
     </row>
     <row r="247">
@@ -15530,7 +15530,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>311.84</v>
+        <v>308.45</v>
       </c>
     </row>
     <row r="248">
@@ -15595,7 +15595,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>105.83</v>
+        <v>104.68</v>
       </c>
     </row>
     <row r="249">
@@ -15656,7 +15656,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>134.92</v>
+        <v>134.59</v>
       </c>
     </row>
     <row r="250">
@@ -15717,7 +15717,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>272.95</v>
+        <v>273.85</v>
       </c>
     </row>
     <row r="251">
@@ -15778,7 +15778,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>434.6</v>
+        <v>435.98</v>
       </c>
     </row>
     <row r="252">
@@ -15839,7 +15839,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>447.76</v>
+        <v>449.18</v>
       </c>
     </row>
     <row r="253">
@@ -15900,7 +15900,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>131.37</v>
+        <v>132.07</v>
       </c>
     </row>
     <row r="254">
@@ -15961,7 +15961,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>938.52</v>
+        <v>943.51</v>
       </c>
     </row>
     <row r="255">
@@ -16022,7 +16022,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>186.99</v>
+        <v>189.66</v>
       </c>
     </row>
     <row r="256">
@@ -16083,7 +16083,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>508.26</v>
+        <v>515.53</v>
       </c>
     </row>
     <row r="257">
@@ -16144,7 +16144,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>161.9</v>
+        <v>164.21</v>
       </c>
     </row>
     <row r="258">
@@ -16205,7 +16205,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>87.28</v>
+        <v>88.53</v>
       </c>
     </row>
     <row r="259">
@@ -16266,7 +16266,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>155.86</v>
+        <v>158.09</v>
       </c>
     </row>
     <row r="260">
@@ -16327,7 +16327,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>322.47</v>
+        <v>326.25</v>
       </c>
     </row>
     <row r="261">
@@ -16388,7 +16388,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>138.82</v>
+        <v>140.44</v>
       </c>
     </row>
     <row r="262">
@@ -16449,7 +16449,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>120.08</v>
+        <v>121.49</v>
       </c>
     </row>
     <row r="263">
@@ -16510,7 +16510,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>171.05</v>
+        <v>173.06</v>
       </c>
     </row>
     <row r="264">
@@ -16571,7 +16571,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>163.81</v>
+        <v>165.73</v>
       </c>
     </row>
     <row r="265">
@@ -16632,7 +16632,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>100.1</v>
+        <v>101.27</v>
       </c>
     </row>
     <row r="266">
@@ -16693,7 +16693,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>142.31</v>
+        <v>143.98</v>
       </c>
     </row>
     <row r="267">
@@ -16754,7 +16754,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>71.15000000000001</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="268">
@@ -16815,7 +16815,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>360.4</v>
+        <v>366.5</v>
       </c>
     </row>
     <row r="269">
@@ -16876,7 +16876,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>171.09</v>
+        <v>173.98</v>
       </c>
     </row>
     <row r="270">
@@ -16937,7 +16937,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>83.27</v>
+        <v>84.68000000000001</v>
       </c>
     </row>
     <row r="271">
@@ -16998,7 +16998,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>247</v>
+        <v>249.51</v>
       </c>
     </row>
     <row r="272">
@@ -17059,7 +17059,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>202.82</v>
+        <v>204.89</v>
       </c>
     </row>
     <row r="273">
@@ -17120,7 +17120,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>818.47</v>
+        <v>826.79</v>
       </c>
     </row>
     <row r="274">
@@ -17181,7 +17181,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>163.69</v>
+        <v>165.36</v>
       </c>
     </row>
     <row r="275">
@@ -17242,7 +17242,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>272.56</v>
+        <v>275.12</v>
       </c>
     </row>
     <row r="276">
@@ -17303,7 +17303,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>250.64</v>
+        <v>248.74</v>
       </c>
     </row>
     <row r="277">
@@ -17364,7 +17364,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>617.27</v>
+        <v>612.59</v>
       </c>
     </row>
     <row r="278">
@@ -17425,7 +17425,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>387.3</v>
+        <v>380.76</v>
       </c>
     </row>
     <row r="279">
@@ -17490,7 +17490,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>118.58</v>
+        <v>116.58</v>
       </c>
     </row>
     <row r="280">
@@ -17551,7 +17551,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>647.91</v>
+        <v>636.96</v>
       </c>
     </row>
     <row r="281">
@@ -17612,7 +17612,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>393.43</v>
+        <v>386.78</v>
       </c>
     </row>
     <row r="282">
@@ -17673,7 +17673,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>213.4</v>
+        <v>209.79</v>
       </c>
     </row>
     <row r="283">
@@ -17734,7 +17734,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>1217.95</v>
+        <v>1200.66</v>
       </c>
     </row>
     <row r="284">
@@ -17795,7 +17795,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>932.75</v>
+        <v>919.51</v>
       </c>
     </row>
     <row r="285">
@@ -17856,7 +17856,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>497.44</v>
+        <v>490.38</v>
       </c>
     </row>
     <row r="286">
@@ -17917,7 +17917,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>253.48</v>
+        <v>249.88</v>
       </c>
     </row>
     <row r="287">
@@ -17978,7 +17978,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>711.64</v>
+        <v>701.86</v>
       </c>
     </row>
     <row r="288">
@@ -18039,7 +18039,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>548.98</v>
+        <v>545.58</v>
       </c>
     </row>
     <row r="289">
@@ -18100,7 +18100,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>888.9400000000001</v>
+        <v>883.4299999999999</v>
       </c>
     </row>
     <row r="290">
@@ -18161,7 +18161,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>877.62</v>
+        <v>881.6</v>
       </c>
     </row>
     <row r="291">
@@ -18222,7 +18222,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>467.61</v>
+        <v>469.73</v>
       </c>
     </row>
     <row r="292">
@@ -18283,7 +18283,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>149.67</v>
+        <v>151.9</v>
       </c>
     </row>
     <row r="293">
@@ -18344,7 +18344,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>327.26</v>
+        <v>334.64</v>
       </c>
     </row>
     <row r="294">
@@ -18405,7 +18405,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>189.4</v>
+        <v>193.67</v>
       </c>
     </row>
     <row r="295">
@@ -18466,7 +18466,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>629.01</v>
+        <v>643.1900000000001</v>
       </c>
     </row>
     <row r="296">
@@ -18527,7 +18527,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>168.54</v>
+        <v>172.34</v>
       </c>
     </row>
     <row r="297">
@@ -18588,7 +18588,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>479.17</v>
+        <v>482.48</v>
       </c>
     </row>
     <row r="298">
@@ -18649,7 +18649,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>247.66</v>
+        <v>249.37</v>
       </c>
     </row>
     <row r="299">
@@ -18710,7 +18710,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>323.18</v>
+        <v>325.41</v>
       </c>
     </row>
     <row r="300">
@@ -18771,7 +18771,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>232.9</v>
+        <v>234.51</v>
       </c>
     </row>
     <row r="301">
@@ -18832,7 +18832,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>540.58</v>
+        <v>542.25</v>
       </c>
     </row>
     <row r="302">
@@ -18893,7 +18893,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>280.42</v>
+        <v>279.68</v>
       </c>
     </row>
     <row r="303">
@@ -18954,7 +18954,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>304.76</v>
+        <v>298.8</v>
       </c>
     </row>
     <row r="304">
@@ -19015,7 +19015,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>304.76</v>
+        <v>298.8</v>
       </c>
     </row>
     <row r="305">
@@ -19076,7 +19076,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>298.91</v>
+        <v>293.06</v>
       </c>
     </row>
     <row r="306">
@@ -19137,7 +19137,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>279.24</v>
+        <v>275.1</v>
       </c>
     </row>
     <row r="307">
@@ -19198,7 +19198,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>99.08</v>
+        <v>99.47</v>
       </c>
     </row>
     <row r="308">
@@ -19259,7 +19259,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>479.05</v>
+        <v>483.86</v>
       </c>
     </row>
     <row r="309">
@@ -19320,7 +19320,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>452.05</v>
+        <v>456.6</v>
       </c>
     </row>
     <row r="310">
@@ -19381,7 +19381,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>120.93</v>
+        <v>122.15</v>
       </c>
     </row>
     <row r="311">
@@ -19442,7 +19442,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>498.3</v>
+        <v>503.29</v>
       </c>
     </row>
     <row r="312">
@@ -19503,7 +19503,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>239.38</v>
+        <v>241.78</v>
       </c>
     </row>
     <row r="313">
@@ -19564,7 +19564,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>160.71</v>
+        <v>161.34</v>
       </c>
     </row>
     <row r="314">
@@ -19625,7 +19625,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>790.34</v>
+        <v>786.34</v>
       </c>
     </row>
     <row r="315">
@@ -19690,7 +19690,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>103.12</v>
+        <v>103.34</v>
       </c>
     </row>
     <row r="316">
@@ -19751,7 +19751,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>136.03</v>
+        <v>136.92</v>
       </c>
     </row>
     <row r="317">
@@ -19812,7 +19812,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>230.72</v>
+        <v>231.25</v>
       </c>
     </row>
     <row r="318">
@@ -19873,7 +19873,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>352.97</v>
+        <v>353.77</v>
       </c>
     </row>
     <row r="319">
@@ -19934,7 +19934,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>311.84</v>
+        <v>313.93</v>
       </c>
     </row>
     <row r="320">
@@ -19995,7 +19995,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>368.45</v>
+        <v>371.03</v>
       </c>
     </row>
     <row r="321">
@@ -20056,7 +20056,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>221.33</v>
+        <v>220.85</v>
       </c>
     </row>
     <row r="322">
@@ -20117,7 +20117,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>256.13</v>
+        <v>255.62</v>
       </c>
     </row>
     <row r="323">
@@ -20178,7 +20178,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>367.14</v>
+        <v>366.41</v>
       </c>
     </row>
     <row r="324">
@@ -20239,7 +20239,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>125.83</v>
+        <v>125.1</v>
       </c>
     </row>
     <row r="325">
@@ -20300,7 +20300,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>473.51</v>
+        <v>470.77</v>
       </c>
     </row>
     <row r="326">
@@ -20361,7 +20361,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>210.58</v>
+        <v>207.19</v>
       </c>
     </row>
     <row r="327">
@@ -20422,7 +20422,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>117.78</v>
+        <v>115.89</v>
       </c>
     </row>
     <row r="328">
@@ -20483,7 +20483,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>260.11</v>
+        <v>255.93</v>
       </c>
     </row>
     <row r="329">
@@ -20544,7 +20544,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>618.53</v>
+        <v>611.33</v>
       </c>
     </row>
     <row r="330">
@@ -20605,7 +20605,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>193.68</v>
+        <v>191.42</v>
       </c>
     </row>
     <row r="331">
@@ -20666,7 +20666,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>206.6</v>
+        <v>204.2</v>
       </c>
     </row>
     <row r="332">
@@ -20727,7 +20727,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>387.6</v>
+        <v>383.09</v>
       </c>
     </row>
     <row r="333">
@@ -20788,7 +20788,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>395.72</v>
+        <v>391.11</v>
       </c>
     </row>
     <row r="334">
@@ -20849,7 +20849,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>217.71</v>
+        <v>215.18</v>
       </c>
     </row>
     <row r="335">
@@ -20910,7 +20910,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>671.8099999999999</v>
+        <v>663.99</v>
       </c>
     </row>
     <row r="336">
@@ -20971,7 +20971,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>211.55</v>
+        <v>209.09</v>
       </c>
     </row>
     <row r="337">
@@ -21032,7 +21032,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>176.63</v>
+        <v>175.65</v>
       </c>
     </row>
     <row r="338">
@@ -21093,7 +21093,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>109.82</v>
+        <v>109.21</v>
       </c>
     </row>
     <row r="339">
@@ -21154,7 +21154,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>67.59</v>
+        <v>67.22</v>
       </c>
     </row>
     <row r="340">
@@ -21215,7 +21215,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>283.5</v>
+        <v>281.93</v>
       </c>
     </row>
     <row r="341">
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>129.66</v>
+        <v>128.94</v>
       </c>
     </row>
     <row r="342">
@@ -21337,7 +21337,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>176.98</v>
+        <v>176</v>
       </c>
     </row>
     <row r="343">
@@ -21398,7 +21398,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>127.45</v>
+        <v>126.74</v>
       </c>
     </row>
     <row r="344">
@@ -21459,7 +21459,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>649.04</v>
+        <v>645.85</v>
       </c>
     </row>
     <row r="345">
@@ -21520,7 +21520,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>111.98</v>
+        <v>112.73</v>
       </c>
     </row>
     <row r="346">
@@ -21581,7 +21581,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>916.14</v>
+        <v>922.27</v>
       </c>
     </row>
     <row r="347">
@@ -21642,7 +21642,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>238.27</v>
+        <v>239.86</v>
       </c>
     </row>
   </sheetData>
